--- a/marketing_forms/007_new_product_evaluation--marketing_forms.xlsx
+++ b/marketing_forms/007_new_product_evaluation--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'customer',_'value':_'customer'}</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Customer', 'value': 'Customer'}</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'employees',_'value':_'employees'}</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Employees', 'value': 'Employees'}</t>
+          <t>Employees</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'label':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'label': 'New', 'value': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'existing',_'value':_'existing'}</t>
+          <t>existing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Existing', 'value': 'Existing'}</t>
+          <t>Existing</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_40,_'label':_'not_yet_launched',_'value':_'not_yet_launched'}</t>
+          <t>not_yet_launched</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 40, 'label': 'Not Yet Launched', 'value': 'Not Yet Launched'}</t>
+          <t>Not Yet Launched</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'launching',_'value':_'launching'}</t>
+          <t>launching</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Launching', 'value': 'Launching'}</t>
+          <t>Launching</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'launched',_'value':_'launched'}</t>
+          <t>launched</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Launched', 'value': 'Launched'}</t>
+          <t>Launched</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_50,_'label':_'customer',_'value':_'customer'}</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 50, 'label': 'Customer', 'value': 'Customer'}</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_51,_'label':_'employees',_'value':_'employees'}</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 51, 'label': 'Employees', 'value': 'Employees'}</t>
+          <t>Employees</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_60,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 60, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_61,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 61, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_62,_'label':_'average',_'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 62, 'label': 'Average', 'value': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_63,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 63, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_64,_'label':_'customer',_'value':_'customer'}</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 64, 'label': 'Customer', 'value': 'Customer'}</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_65,_'label':_'employees',_'value':_'employees'}</t>
+          <t>employees</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 65, 'label': 'Employees', 'value': 'Employees'}</t>
+          <t>Employees</t>
         </is>
       </c>
     </row>
